--- a/ACCTG522/datasets/01_scavenger_hunt/file-1.xlsx
+++ b/ACCTG522/datasets/01_scavenger_hunt/file-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\teaching\320_2022-23_fall\teaching_notes\class_2\files\file_scavenger_hunt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github_connections\datasets.io\ACCTG522\datasets\01_scavenger_hunt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7D6402-F5E3-4971-AB06-3BF54756E591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2B912C-357A-419C-8AEA-6CE1A828AD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="57600" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5145" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Research</t>
+      <t xml:space="preserve"> Welcome</t>
     </r>
   </si>
 </sst>
